--- a/01_智谱专题研究/评分/测试一评分结果.xlsx
+++ b/01_智谱专题研究/评分/测试一评分结果.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合结果" sheetId="1" r:id="Rc4660a34c60847b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分明细" sheetId="2" r:id="Rb1bde006b94c4243"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事实抽检" sheetId="3" r:id="R1eae7ba65f8940c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="4" r:id="Rb6ab306b69684ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合结果" sheetId="1" r:id="Rfde1a17b9d97459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分明细" sheetId="2" r:id="R9e36f7421fdb4563"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事实抽检" sheetId="3" r:id="Rbc985e41c4704aa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="4" r:id="Rf178c8b262fb41a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计记录" sheetId="5" r:id="Rd91f654c8a834e4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,12 +17,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0.00"/>
     <x:numFmt numFmtId="201" formatCode="0.0"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="203" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -47,6 +49,12 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -84,7 +92,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -115,6 +123,11 @@
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -349,7 +362,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>评分日期：2026-08-04；效率不纳入质量总分。</x:v>
+        <x:v>评分日期：2026-08-04；效率纳入质量总分，工作流交付为准入项。</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -387,19 +400,19 @@
         <x:v>研究完整性</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
+        <x:v>分析观点</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
         <x:v>来源与引用</x:v>
       </x:c>
-      <x:c r="I4" s="6" t="str">
-        <x:v>工作流交付</x:v>
-      </x:c>
       <x:c r="J4" s="6" t="str">
-        <x:v>分析观点</x:v>
+        <x:v>效率分</x:v>
       </x:c>
       <x:c r="K4" s="6" t="str">
         <x:v>质量总分</x:v>
       </x:c>
       <x:c r="L4" s="6" t="str">
-        <x:v>每分钟质量分</x:v>
+        <x:v>工作流交付</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -422,24 +435,24 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="G5" s="2" t="n">
-        <x:v>92.6</x:v>
+        <x:v>92.81818181818181</x:v>
       </x:c>
       <x:c r="H5" s="2" t="n">
-        <x:v>97.25</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I5" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>94.91666666666667</x:v>
       </x:c>
       <x:c r="J5" s="2" t="n">
-        <x:v>97.5</x:v>
+        <x:f>100*SQRT(MIN($D$5:$D$7)/D5)</x:f>
+        <x:v>79.72962796809188</x:v>
       </x:c>
       <x:c r="K5" s="2" t="n">
         <x:f>SUMIF('评分明细'!$A$2:$A$16,B5,'评分明细'!$E$2:$E$16)</x:f>
-        <x:v>95.845</x:v>
-      </x:c>
-      <x:c r="L5" s="2" t="n">
-        <x:f>K5/E5</x:f>
-        <x:v>12.806939402712514</x:v>
+        <x:v>92.8100840089304</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>合格</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -462,24 +475,24 @@
         <x:v>93.33333333333333</x:v>
       </x:c>
       <x:c r="G6" s="2" t="n">
-        <x:v>81.8</x:v>
+        <x:v>81.88888888888889</x:v>
       </x:c>
       <x:c r="H6" s="2" t="n">
-        <x:v>96.75</x:v>
+        <x:v>82.5</x:v>
       </x:c>
       <x:c r="I6" s="2" t="n">
+        <x:v>95.75</x:v>
+      </x:c>
+      <x:c r="J6" s="2" t="n">
+        <x:f>100*SQRT(MIN($D$5:$D$7)/D6)</x:f>
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="J6" s="2" t="n">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="K6" s="2" t="n">
         <x:f>SUMIF('评分明细'!$A$2:$A$16,B6,'评分明细'!$E$2:$E$16)</x:f>
-        <x:v>90.37666666666667</x:v>
-      </x:c>
-      <x:c r="L6" s="2" t="n">
-        <x:f>K6/E6</x:f>
-        <x:v>18.997337443946186</x:v>
+        <x:v>88.64166666666667</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>合格</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -502,24 +515,24 @@
         <x:v>86.66666666666667</x:v>
       </x:c>
       <x:c r="G7" s="2" t="n">
-        <x:v>98.4</x:v>
+        <x:v>98.33333333333334</x:v>
       </x:c>
       <x:c r="H7" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>77.5</x:v>
       </x:c>
       <x:c r="I7" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>70.25</x:v>
       </x:c>
       <x:c r="J7" s="2" t="n">
-        <x:v>82.5</x:v>
+        <x:f>100*SQRT(MIN($D$5:$D$7)/D7)</x:f>
+        <x:v>56.51344972857151</x:v>
       </x:c>
       <x:c r="K7" s="2" t="n">
         <x:f>SUMIF('评分明细'!$A$2:$A$16,B7,'评分明细'!$E$2:$E$16)</x:f>
-        <x:v>87.38833333333334</x:v>
-      </x:c>
-      <x:c r="L7" s="2" t="n">
-        <x:f>K7/E7</x:f>
-        <x:v>5.866695011972162</x:v>
+        <x:v>83.67634497285715</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>合格</x:v>
       </x:c>
     </x:row>
     <x:row r="8"/>
@@ -609,13 +622,13 @@
         <x:v>事实可靠性</x:v>
       </x:c>
       <x:c r="C2" s="15" t="n">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="16" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E2" s="16" t="n">
-        <x:v>33.25</x:v>
+        <x:v>28.5</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
         <x:v>30 条分层事实抽检</x:v>
@@ -629,56 +642,56 @@
         <x:v>研究完整性</x:v>
       </x:c>
       <x:c r="C3" s="15" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="16" t="n">
-        <x:v>92.6</x:v>
+        <x:v>92.81818181818181</x:v>
       </x:c>
       <x:c r="E3" s="16" t="n">
-        <x:v>18.52</x:v>
+        <x:v>27.845454545454544</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
         <x:v>模型覆盖率占 60%，字段覆盖率占 40%</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="14" t="str">
         <x:v>ChatGPT Work</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>来源与引用</x:v>
+        <x:v>分析观点</x:v>
       </x:c>
       <x:c r="C4" s="15" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="16" t="n">
-        <x:v>97.25</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E4" s="16" t="n">
-        <x:v>19.45</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>20 条引用抽查：有效性、支持关系、一手来源比例、冲突处理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+        <x:v>策略判断、事实与推断区分、竞争位置、后续跟踪框架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A5" s="14" t="str">
         <x:v>ChatGPT Work</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>工作流交付</x:v>
+        <x:v>来源与引用</x:v>
       </x:c>
       <x:c r="C5" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="16" t="n">
-        <x:v>100</x:v>
+        <x:v>94.91666666666667</x:v>
       </x:c>
       <x:c r="E5" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>9.491666666666667</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>五项指定交付物、表头、事实编号、PPT 页数、风险提示</x:v>
+        <x:v>20 条引用抽查：有效性、支持关系、一手来源比例、冲突处理</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -686,19 +699,19 @@
         <x:v>ChatGPT Work</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>分析观点</x:v>
+        <x:v>效率</x:v>
       </x:c>
       <x:c r="C6" s="15" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="16" t="n">
-        <x:v>97.5</x:v>
+        <x:v>79.72962796809188</x:v>
       </x:c>
       <x:c r="E6" s="16" t="n">
-        <x:v>14.625</x:v>
+        <x:v>7.972962796809188</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>策略判断、事实与推断区分、竞争位置、后续跟踪框架</x:v>
+        <x:v>效率分 = 100 × √（最快总耗时 ÷ 本平台总耗时）</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -709,13 +722,13 @@
         <x:v>事实可靠性</x:v>
       </x:c>
       <x:c r="C7" s="15" t="n">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="16" t="n">
         <x:v>93.33333333333333</x:v>
       </x:c>
       <x:c r="E7" s="16" t="n">
-        <x:v>32.666666666666664</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
         <x:v>30 条分层事实抽检</x:v>
@@ -729,56 +742,56 @@
         <x:v>研究完整性</x:v>
       </x:c>
       <x:c r="C8" s="15" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="16" t="n">
-        <x:v>81.8</x:v>
+        <x:v>81.88888888888889</x:v>
       </x:c>
       <x:c r="E8" s="16" t="n">
-        <x:v>16.36</x:v>
+        <x:v>24.566666666666666</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
         <x:v>模型覆盖率占 60%，字段覆盖率占 40%</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="14" t="str">
         <x:v>TRAE Work</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>来源与引用</x:v>
+        <x:v>分析观点</x:v>
       </x:c>
       <x:c r="C9" s="15" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="16" t="n">
-        <x:v>96.75</x:v>
+        <x:v>82.5</x:v>
       </x:c>
       <x:c r="E9" s="16" t="n">
-        <x:v>19.35</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>20 条引用抽查：有效性、支持关系、一手来源比例、冲突处理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+        <x:v>策略判断、事实与推断区分、竞争位置、后续跟踪框架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A10" s="14" t="str">
         <x:v>TRAE Work</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>工作流交付</x:v>
+        <x:v>来源与引用</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D10" s="16" t="n">
-        <x:v>100</x:v>
+        <x:v>95.75</x:v>
       </x:c>
       <x:c r="E10" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>9.575</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>五项指定交付物、表头、事实编号、PPT 页数、风险提示</x:v>
+        <x:v>20 条引用抽查：有效性、支持关系、一手来源比例、冲突处理</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -786,19 +799,19 @@
         <x:v>TRAE Work</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>分析观点</x:v>
+        <x:v>效率</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="16" t="n">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E11" s="16" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>策略判断、事实与推断区分、竞争位置、后续跟踪框架</x:v>
+        <x:v>效率分 = 100 × √（最快总耗时 ÷ 本平台总耗时）</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -809,13 +822,13 @@
         <x:v>事实可靠性</x:v>
       </x:c>
       <x:c r="C12" s="15" t="n">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="16" t="n">
         <x:v>86.66666666666667</x:v>
       </x:c>
       <x:c r="E12" s="16" t="n">
-        <x:v>30.333333333333336</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
         <x:v>30 条分层事实抽检</x:v>
@@ -829,56 +842,56 @@
         <x:v>研究完整性</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="16" t="n">
-        <x:v>98.4</x:v>
+        <x:v>98.33333333333334</x:v>
       </x:c>
       <x:c r="E13" s="16" t="n">
-        <x:v>19.68</x:v>
+        <x:v>29.500000000000004</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
         <x:v>模型覆盖率占 60%，字段覆盖率占 40%</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="14" t="str">
         <x:v>WorkBuddy</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>来源与引用</x:v>
+        <x:v>分析观点</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="16" t="n">
-        <x:v>75</x:v>
+        <x:v>77.5</x:v>
       </x:c>
       <x:c r="E14" s="16" t="n">
-        <x:v>15</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>20 条引用抽查：有效性、支持关系、一手来源比例、冲突处理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
+        <x:v>策略判断、事实与推断区分、竞争位置、后续跟踪框架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" s="14" t="str">
         <x:v>WorkBuddy</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>工作流交付</x:v>
+        <x:v>来源与引用</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D15" s="16" t="n">
-        <x:v>100</x:v>
+        <x:v>70.25</x:v>
       </x:c>
       <x:c r="E15" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>7.025</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>五项指定交付物、表头、事实编号、PPT 页数、风险提示</x:v>
+        <x:v>20 条引用抽查：有效性、支持关系、一手来源比例、冲突处理</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -886,19 +899,19 @@
         <x:v>WorkBuddy</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>分析观点</x:v>
+        <x:v>效率</x:v>
       </x:c>
       <x:c r="C16" s="15" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="16" t="n">
-        <x:v>82.5</x:v>
+        <x:v>56.51344972857151</x:v>
       </x:c>
       <x:c r="E16" s="16" t="n">
-        <x:v>12.375</x:v>
+        <x:v>5.65134497285715</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>策略判断、事实与推断区分、竞争位置、后续跟踪框架</x:v>
+        <x:v>效率分 = 100 × √（最快总耗时 ÷ 本平台总耗时）</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3860,82 +3873,390 @@
         <x:v>质量总分</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>事实可靠性 35% + 研究完整性 20% + 来源与引用 20% + 工作流交付 10% + 分析观点 15%。</x:v>
+        <x:v>事实可靠性 30% + 研究完整性 30% + 分析观点 20% + 来源与引用 10% + 效率 10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="14" t="str">
-        <x:v>事实判断</x:v>
+        <x:v>准入项</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>正确=1；部分正确=0.5；错误=0。</x:v>
+        <x:v>五项指定交付物齐全、可复核记为合格；有明显缺失记为不合格/需补交。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="14" t="str">
-        <x:v>抽检构成</x:v>
+        <x:v>事实判断</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>每家 30 条，按七类事实分层。</x:v>
+        <x:v>正确=1；部分正确=0.5；错误=0。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>效率</x:v>
+        <x:v>抽检构成</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>总耗时、每分钟质量分仅作效率观察，不计入质量总分。</x:v>
+        <x:v>每家 30 条，按七类事实分层。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="14" t="str">
-        <x:v>来源</x:v>
+        <x:v>效率</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>优先官方文档、技术报告、官方仓库、模型卡；媒体与第三方仅作为补充。</x:v>
+        <x:v>效率分 = 100 × √（最快总耗时 ÷ 本平台总耗时）。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>日期</x:v>
+        <x:v>来源</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>区分首发日、官网里程碑日、报道日。</x:v>
+        <x:v>优先官方文档、技术报告、官方仓库、模型卡；媒体与第三方仅作为补充。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="14" t="str">
-        <x:v>价格</x:v>
+        <x:v>日期</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>必须标注站点、币种、生效时间。</x:v>
+        <x:v>区分首发日、官网里程碑日、报道日。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="14" t="str">
-        <x:v>Benchmark</x:v>
+        <x:v>价格</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>区分官方自评、第三方榜单和可复现实验。</x:v>
+        <x:v>必须标注站点、币种、生效时间。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="14" t="str">
-        <x:v>边界</x:v>
+        <x:v>Benchmark</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>单次任务与当前平台设置下的比较，不等同于底层模型绝对能力比较。</x:v>
+        <x:v>区分官方自评、第三方榜单和可复现实验。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>文件</x:v>
+        <x:v>边界</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>原始输出保持不改；本工作簿和同目录 CSV/MD 为评分成果。</x:v>
+        <x:v>端到端耗时受网络、平台调度和工具链影响，不等同于底层模型纯推理速度。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>来源与引用审计</x:v>
+      </x:c>
+      <x:c r="B1" s="19"/>
+      <x:c r="C1" s="19"/>
+      <x:c r="D1" s="19"/>
+      <x:c r="E1" s="19"/>
+      <x:c r="F1" s="19"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Agent</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>有效链接/20</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>直接支持/20</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>一手来源/20</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>已处理冲突/应处理冲突</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>来源与引用分</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>ChatGPT Work</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>20/20</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>19/20</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>20/20</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="str">
+        <x:v>2/3</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="n">
+        <x:v>94.91666666666667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>TRAE Work</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>20/20</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>19/20</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>20/20</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>3/4</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="n">
+        <x:v>95.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>WorkBuddy</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>18/20</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>16/20</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>11/20</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>2/4</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="n">
+        <x:v>70.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6"/>
+    <x:row r="7" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A7" s="19" t="str">
+        <x:v>研究完整性审计</x:v>
+      </x:c>
+      <x:c r="B7" s="19"/>
+      <x:c r="C7" s="19"/>
+      <x:c r="D7" s="19"/>
+      <x:c r="E7" s="19"/>
+      <x:c r="F7" s="19"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>Agent</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>已覆盖核心家族</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>模型家族覆盖率</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>完成字段/应填字段</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>字段覆盖率</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>研究完整性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>ChatGPT Work</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>11/12</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="n">
+        <x:v>91.66666666666666</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>104/110</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="n">
+        <x:v>94.54545454545455</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="n">
+        <x:v>92.81818181818181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>TRAE Work</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>9/12</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>83/90</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="n">
+        <x:v>92.22222222222223</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="n">
+        <x:v>81.88888888888889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>WorkBuddy</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>12/12</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D11" s="20" t="str">
+        <x:v>115/120</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="n">
+        <x:v>95.83333333333334</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="n">
+        <x:v>98.33333333333334</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12"/>
+    <x:row r="13" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A13" s="19" t="str">
+        <x:v>分析观点审计</x:v>
+      </x:c>
+      <x:c r="B13" s="19"/>
+      <x:c r="C13" s="19"/>
+      <x:c r="D13" s="19"/>
+      <x:c r="E13" s="19"/>
+      <x:c r="F13" s="19"/>
+      <x:c r="G13" s="19"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>Agent</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>模型策略判断</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>事实与推断区分</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>竞争位置判断</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>后续跟踪框架</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>原始分/20</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>分析观点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>ChatGPT Work</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="E15" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F15" s="2" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>TRAE Work</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="n">
+        <x:v>82.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>WorkBuddy</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="F17" s="2" t="n">
+        <x:v>15.5</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="n">
+        <x:v>77.5</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A7:G7"/>
+    <x:mergeCell ref="A13:G13"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>